--- a/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACCFB77A-4F43-4AE2-A2D0-9E154509547A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DA6A12E-4F47-413A-BCF7-BFDB8E9F78B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -40,6 +40,32 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{2FF9EF2B-EBD7-4C7E-9F26-8FF1228838F5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+11-09-2025
+AFS will be sufficient
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D8" authorId="0" shapeId="0" xr:uid="{79577DE7-359E-49C1-A1D9-EC64BAD436CB}">
       <text>
         <r>
@@ -97,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="92">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -294,9 +320,6 @@
     <t>UCE_max nuclear capacity</t>
   </si>
   <si>
-    <t>UC_RHSRT~2050</t>
-  </si>
-  <si>
     <t>life</t>
   </si>
   <si>
@@ -357,6 +380,15 @@
     <t>wind*</t>
   </si>
   <si>
+    <t>~UC_T: 2050</t>
+  </si>
+  <si>
+    <t>base-year nuclear capacity</t>
+  </si>
+  <si>
+    <t>\I: hydro</t>
+  </si>
+  <si>
     <t>windon</t>
   </si>
   <si>
@@ -376,7 +408,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,8 +458,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,6 +492,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -474,13 +527,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -491,10 +545,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
     <cellStyle name="Heading 4" xfId="3" builtinId="19"/>
+    <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -867,7 +924,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="AD1">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.45">
@@ -937,15 +994,12 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="4">
-        <f>IFERROR(VLOOKUP(B5,$F$3:$J$11,5,FALSE),"")</f>
-        <v>0.2662402976913299</v>
-      </c>
+      <c r="D5" s="4"/>
       <c r="F5" t="s">
         <v>8</v>
       </c>
@@ -963,7 +1017,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -996,7 +1050,7 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -1130,7 +1184,7 @@
       </c>
       <c r="AJ8">
         <f>AI8*$AD$1</f>
-        <v>0.16837899543378995</v>
+        <v>3.7417554540842217E-2</v>
       </c>
       <c r="AK8">
         <v>0</v>
@@ -1198,7 +1252,7 @@
       </c>
       <c r="AJ9">
         <f>AI9*$AD$1</f>
-        <v>0.1386884174405621</v>
+        <v>3.0819648320124911E-2</v>
       </c>
       <c r="AK9">
         <v>0</v>
@@ -1209,7 +1263,7 @@
     </row>
     <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3">
         <v>0.21274387712743878</v>
@@ -1235,7 +1289,7 @@
         <v>26</v>
       </c>
       <c r="U13" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.45">
@@ -1275,9 +1329,6 @@
       <c r="AC14" t="s">
         <v>17</v>
       </c>
-      <c r="AD14" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
@@ -1291,7 +1342,7 @@
         <v>Hydropower - large-scale unit,Solar photovoltaics - Large scale unit,Wind offshore,Wind onshore</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U15" t="s">
         <v>64</v>
@@ -1303,15 +1354,18 @@
         <v>1</v>
       </c>
       <c r="AB15">
-        <f>SUMIFS(historical_data_long!$D$3:$D$626,historical_data_long!$A$3:$A$626,Veda!$V15,historical_data_long!$C$3:$C$626,"GW",historical_data_long!$B$3:$B$626,2022)</f>
+        <f>AE15*2.5</f>
         <v>0</v>
       </c>
       <c r="AC15">
         <v>3</v>
       </c>
-      <c r="AD15">
-        <f>AB15*2.5</f>
-        <v>0</v>
+      <c r="AE15" s="11">
+        <f>SUMIFS(historical_data_long!$D$3:$D$626,historical_data_long!$A$3:$A$626,Veda!$V15,historical_data_long!$C$3:$C$626,"GW",historical_data_long!$B$3:$B$626,2022)</f>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.45">
@@ -1453,24 +1507,24 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28">
         <v>50</v>
       </c>
       <c r="G28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29">
         <v>8.76</v>
       </c>
       <c r="G29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.45">
@@ -1533,7 +1587,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.45">
       <c r="D40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E40">
         <v>-1</v>
@@ -1541,7 +1595,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1564,41 +1619,41 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" t="s">
         <v>70</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>71</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>72</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>73</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>74</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>75</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>76</v>
-      </c>
-      <c r="J10" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -1632,7 +1687,7 @@
     </row>
     <row r="18" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -1640,16 +1695,16 @@
         <v>48</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="F19" s="8">
         <v>2025</v>
@@ -1674,7 +1729,7 @@
         <v>solar</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1704,7 +1759,7 @@
         <v>wind*</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1734,7 +1789,7 @@
         <v>hydro</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1764,7 +1819,7 @@
         <v>nuclear</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1919,7 +1974,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B10">
         <v>2000</v>
@@ -2045,7 +2100,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B19">
         <v>2001</v>
@@ -2171,7 +2226,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28">
         <v>2002</v>
@@ -2297,7 +2352,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B37">
         <v>2003</v>
@@ -2423,7 +2478,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B46">
         <v>2004</v>
@@ -2549,7 +2604,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B55">
         <v>2005</v>
@@ -2675,7 +2730,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B64">
         <v>2006</v>
@@ -2801,7 +2856,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B73">
         <v>2007</v>
@@ -2927,7 +2982,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B82">
         <v>2008</v>
@@ -3053,7 +3108,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B91">
         <v>2009</v>
@@ -3179,7 +3234,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B100">
         <v>2010</v>
@@ -3305,7 +3360,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B109">
         <v>2011</v>
@@ -3431,7 +3486,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B118">
         <v>2012</v>
@@ -3557,7 +3612,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B127">
         <v>2013</v>
@@ -3683,7 +3738,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B136">
         <v>2014</v>
@@ -3809,7 +3864,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B145">
         <v>2015</v>
@@ -3935,7 +3990,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B154">
         <v>2016</v>
@@ -4061,7 +4116,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B163">
         <v>2017</v>
@@ -4187,7 +4242,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B172">
         <v>2018</v>
@@ -4313,7 +4368,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B181">
         <v>2019</v>
@@ -4439,7 +4494,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B190">
         <v>2020</v>
@@ -4565,7 +4620,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B199">
         <v>2021</v>
@@ -4691,7 +4746,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B208">
         <v>2022</v>
@@ -4817,7 +4872,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B217">
         <v>2023</v>
@@ -4937,7 +4992,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B226">
         <v>2000</v>
@@ -5057,7 +5112,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B235">
         <v>2001</v>
@@ -5177,7 +5232,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B244">
         <v>2002</v>
@@ -5297,7 +5352,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B253">
         <v>2003</v>
@@ -5417,7 +5472,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B262">
         <v>2004</v>
@@ -5537,7 +5592,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B271">
         <v>2005</v>
@@ -5657,7 +5712,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B280">
         <v>2006</v>
@@ -5777,7 +5832,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B289">
         <v>2007</v>
@@ -5897,7 +5952,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B298">
         <v>2008</v>
@@ -6017,7 +6072,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B307">
         <v>2009</v>
@@ -6137,7 +6192,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B316">
         <v>2010</v>
@@ -6257,7 +6312,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B325">
         <v>2011</v>
@@ -6377,7 +6432,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B334">
         <v>2012</v>
@@ -6497,7 +6552,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B343">
         <v>2013</v>
@@ -6617,7 +6672,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B352">
         <v>2014</v>
@@ -6737,7 +6792,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B361">
         <v>2015</v>
@@ -6857,7 +6912,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B370">
         <v>2016</v>
@@ -6977,7 +7032,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B379">
         <v>2017</v>
@@ -7097,7 +7152,7 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B388">
         <v>2018</v>
@@ -7217,7 +7272,7 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B397">
         <v>2019</v>
@@ -7337,7 +7392,7 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B406">
         <v>2020</v>
@@ -7457,7 +7512,7 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B415">
         <v>2021</v>
@@ -7577,7 +7632,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B424">
         <v>2022</v>
@@ -7697,7 +7752,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B433">
         <v>2023</v>
@@ -7823,7 +7878,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B442">
         <v>2000</v>
@@ -7949,7 +8004,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B451">
         <v>2001</v>
@@ -8075,7 +8130,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B460">
         <v>2002</v>
@@ -8201,7 +8256,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B469">
         <v>2003</v>
@@ -8327,7 +8382,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B478">
         <v>2004</v>
@@ -8453,7 +8508,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B487">
         <v>2005</v>
@@ -8579,7 +8634,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B496">
         <v>2006</v>
@@ -8705,7 +8760,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B505">
         <v>2007</v>
@@ -8831,7 +8886,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B514">
         <v>2008</v>
@@ -8957,7 +9012,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B523">
         <v>2009</v>
@@ -9083,7 +9138,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B532">
         <v>2010</v>
@@ -9209,7 +9264,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B541">
         <v>2011</v>
@@ -9335,7 +9390,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B550">
         <v>2012</v>
@@ -9461,7 +9516,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B559">
         <v>2013</v>
@@ -9587,7 +9642,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B568">
         <v>2014</v>
@@ -9713,7 +9768,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B577">
         <v>2015</v>
@@ -9839,7 +9894,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B586">
         <v>2016</v>
@@ -9965,7 +10020,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B595">
         <v>2017</v>
@@ -10091,7 +10146,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B604">
         <v>2018</v>
@@ -10217,7 +10272,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B613">
         <v>2019</v>
@@ -10343,7 +10398,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B622">
         <v>2020</v>
@@ -10469,7 +10524,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B631">
         <v>2021</v>
@@ -10595,7 +10650,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B640">
         <v>2022</v>
@@ -10721,7 +10776,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B649">
         <v>2023</v>

--- a/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DA6A12E-4F47-413A-BCF7-BFDB8E9F78B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6D373C1-CCEB-417E-B132-5517C87740E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6D373C1-CCEB-417E-B132-5517C87740E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A0A40B5-129D-4E54-A9D8-5950D4C6361A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A0A40B5-129D-4E54-A9D8-5950D4C6361A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3430CB63-07EE-4802-91AE-8B75599E0AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3430CB63-07EE-4802-91AE-8B75599E0AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D304A42-B9DF-480F-B42F-276EAA0C8B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D304A42-B9DF-480F-B42F-276EAA0C8B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5DB1F26-8DC8-4AEA-84BB-48EA13BB0248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_GRC/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5DB1F26-8DC8-4AEA-84BB-48EA13BB0248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E7E32F5-D29C-47A5-BC6D-9FBDC141C0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
